--- a/Assignment 17/Global_Superstore_questions.xlsx
+++ b/Assignment 17/Global_Superstore_questions.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28014"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Noman Traders\Desktop\DS B2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MY COMPUTER\Desktop\Assignments B5 Sec B\Assignment 17\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426F1FB2-97D2-40A9-84DD-3675969357F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Questions" sheetId="1" r:id="rId1"/>
@@ -186,7 +187,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -536,9 +537,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -546,7 +547,7 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -560,7 +561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -574,7 +575,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -588,7 +589,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -602,7 +603,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -616,7 +617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -630,7 +631,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -644,7 +645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -658,7 +659,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -672,7 +673,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -686,7 +687,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -700,7 +701,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -714,7 +715,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -728,7 +729,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -742,7 +743,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -756,7 +757,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -770,7 +771,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -784,7 +785,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -798,7 +799,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -812,7 +813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -826,20 +827,20 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D20"/>
+  <autoFilter ref="A1:D20" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Assignment 17/Global_Superstore_questions.xlsx
+++ b/Assignment 17/Global_Superstore_questions.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28014"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MY COMPUTER\Desktop\Assignments B5 Sec B\Assignment 17\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Noman Traders\Desktop\DS B2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426F1FB2-97D2-40A9-84DD-3675969357F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
   </bookViews>
   <sheets>
     <sheet name="Questions" sheetId="1" r:id="rId1"/>
@@ -187,7 +186,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -537,9 +536,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -547,7 +546,7 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,7 +560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -575,7 +574,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -589,7 +588,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -603,7 +602,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -617,7 +616,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -631,7 +630,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -645,7 +644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -659,7 +658,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -673,7 +672,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -687,7 +686,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -701,7 +700,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -715,7 +714,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -729,7 +728,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -743,7 +742,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -757,7 +756,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -771,7 +770,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -785,7 +784,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -799,7 +798,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -813,7 +812,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -827,20 +826,20 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D20" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:D20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>